--- a/src/main/resources/static/template_exel/zones-livraison/template_import_zones_livraison.xlsx
+++ b/src/main/resources/static/template_exel/zones-livraison/template_import_zones_livraison.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t>libelle</t>
   </si>
@@ -25,7 +25,7 @@
     <t>prix</t>
   </si>
   <si>
-    <t>Hell-Ville Center-1</t>
+    <t>Hell-Ville Center</t>
   </si>
   <si>
     <t>0.000</t>
@@ -37,6 +37,24 @@
     <t>5000.00</t>
   </si>
   <si>
+    <t>Ambatoloaka / Madirokely</t>
+  </si>
+  <si>
+    <t>15.000</t>
+  </si>
+  <si>
+    <t>10000.00</t>
+  </si>
+  <si>
+    <t>Andilana</t>
+  </si>
+  <si>
+    <t>30.000</t>
+  </si>
+  <si>
+    <t>25000.00</t>
+  </si>
+  <si>
     <t>Dzamandzar</t>
   </si>
   <si>
@@ -56,6 +74,39 @@
   </si>
   <si>
     <t>8000.00</t>
+  </si>
+  <si>
+    <t>Ampasindava</t>
+  </si>
+  <si>
+    <t>10.000</t>
+  </si>
+  <si>
+    <t>20.000</t>
+  </si>
+  <si>
+    <t>15000.00</t>
+  </si>
+  <si>
+    <t>Nosy Be Centre</t>
+  </si>
+  <si>
+    <t>3.000</t>
+  </si>
+  <si>
+    <t>3000.00</t>
+  </si>
+  <si>
+    <t>Aéroport</t>
+  </si>
+  <si>
+    <t>2.000</t>
+  </si>
+  <si>
+    <t>8.000</t>
+  </si>
+  <si>
+    <t>7000.00</t>
   </si>
 </sst>
 </file>
@@ -486,7 +537,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>9</v>
@@ -500,20 +551,85 @@
         <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="2" t="s">
+    </row>
+    <row r="5" ht="12.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" ht="12.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" ht="12.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" ht="12.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
